--- a/files/AUTOM_08_Sustainability_ESG.xlsx
+++ b/files/AUTOM_08_Sustainability_ESG.xlsx
@@ -7,9 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emissions Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EV Transition KPIs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR Report Snippets" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,22 +26,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="000E7490"/>
-      <sz val="14"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00666666"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,7 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E7490"/>
+        <fgColor rgb="001F2D55"/>
+        <bgColor rgb="001F2D55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F6FB"/>
+        <bgColor rgb="00F4F6FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,35 +79,50 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00D0D7E2"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00D0D7E2"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00D0D7E2"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00D0D7E2"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -461,450 +489,907 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zava Motors – GHG Emissions Inventory FY25</t>
+          <t>AUTOM 08 Sustainability ESG</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scope 1, 2, 3 emissions across business segments | Unit: tCO2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
+          <t>Source file: AUTOM_08_Sustainability_ESG.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Segment</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Scope 1 (Direct)</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Scope 2 (Electricity)</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Scope 3 (Value Chain)</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Total tCO2e</t>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Dealership Network (266 outlets)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>1240</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>8920</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>4180</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>14340</v>
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 01</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>39899.42</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Rental Fleet Operations (Zava Rent)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>18400</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>1120</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>6200</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>25720</v>
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 02</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>93232</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Spare Parts Warehousing &amp; Logistics</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>980</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>1450</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>3100</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>5530</v>
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 03</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>43202.59</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Head Office &amp; Regional Offices</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>1980</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>540</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>2600</v>
+      <c r="A8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 04</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>150880.82</v>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Auction &amp; Yard Operations (Zava Auctions)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>320</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>410</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>280</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>1010</v>
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 05</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>238305.2</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Financed Emissions (JACCS – customer 2W)</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>412000</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>412000</v>
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 06</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>319389.11</v>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 07</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>79179.03</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 08</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>460554.35</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 09</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>298946.36</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 10</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>13549.69</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 11</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>260187.01</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 12</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>451504.11</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 13</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>159740.91</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 14</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>296701.35</v>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Tracking on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 15</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>167659.33</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 16</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>54280.98</v>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 17</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>220956.63</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 18</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>352294.17</v>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 19</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>88319.38</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 20</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>308847.76</v>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Tracking on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 21</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>240427.51</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 22</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>446009.31</v>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 23</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>300987.43</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 24</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>198059.8</v>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 25</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>303546.63</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 26</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>361335.06</v>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 27</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>51930.22</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 28</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>382208.63</v>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 29</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>222484.81</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>AUTOM 08 Sustainability ESG — line item 30</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>403357.17</v>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Electric 2-Wheeler &amp; EV Mobility Transition Targets</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Initiative</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>FY25 Actual</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>FY26 Target</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FY30 Target</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>EV motorcycles sold (units/yr)</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>1180</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>4500</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>28000</v>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>On track</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Dealers EV-service-certified (%)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Below plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Rental fleet electrified (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>On track</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Battery swap stations (count)</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Pilot phase</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Scope 1+2 reduction vs FY22 (%)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>On track</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Green financing % of book (JACCS)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Corporate Responsibility Report – Draft Narrative Blocks</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Theme</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Narrative</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Climate &amp; Mobility Transition</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>In FY25, Zava Motors accelerated its mobility transition, expanding the EV-ready dealer footprint by 3x and piloting 6 battery swap stations across Surabaya and Malang. We remain committed to a 50% Scope 1+2 reduction by FY30 vs FY22 baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="75" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Road Safety &amp; Rider Welfare</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Our 266 Honda dealerships delivered free safety inspections to 142,000 riders. We launched a financing-linked safety rider program with JACCS, embedding road-safety training into loan onboarding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="75" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Community &amp; Financial Inclusion</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Through JACCS Finance JV, we extended IDR 480B of inclusive 2-wheeler financing to first-time formal-sector borrowers in East Java and East Nusa Tenggara, with a 96% on-time repayment rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="75" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Governance &amp; PDPA Compliance</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>All customer data across dealerships, rental, insurance, and financing operates under a unified PDPA-aligned data governance framework. Zero material data incidents reported in FY25.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
